--- a/LISTAS_ORDENADAS/MA/Herrajes/RUEDAS IMPORTADAS.xlsx
+++ b/LISTAS_ORDENADAS/MA/Herrajes/RUEDAS IMPORTADAS.xlsx
@@ -888,14 +888,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45216.53896770441</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="19.5" customHeight="1" s="22">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -937,13 +933,6 @@
       <c r="A11" s="26" t="n"/>
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="18" customHeight="1" s="22">
       <c r="A19" s="12" t="inlineStr">
         <is>
@@ -975,7 +964,7 @@
       </c>
       <c r="C20" s="19" t="n"/>
       <c r="D20" s="5" t="n">
-        <v>347.22</v>
+        <v>286.964</v>
       </c>
       <c r="E20" s="14" t="n"/>
     </row>
@@ -992,7 +981,7 @@
       </c>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="7" t="n">
-        <v>385.06</v>
+        <v>318.234</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="22">
@@ -1008,7 +997,7 @@
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="5" t="n">
-        <v>496.59</v>
+        <v>410.406</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="22">
@@ -1024,7 +1013,7 @@
       </c>
       <c r="C23" s="19" t="n"/>
       <c r="D23" s="7" t="n">
-        <v>744.88</v>
+        <v>615.6079999999999</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="22">
@@ -1040,7 +1029,7 @@
       </c>
       <c r="C24" s="19" t="n"/>
       <c r="D24" s="5" t="n">
-        <v>1489.74</v>
+        <v>1231.196</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="22">
@@ -1056,7 +1045,7 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="5" t="n">
-        <v>1788.47</v>
+        <v>1478.077</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="22">
@@ -1072,7 +1061,7 @@
       </c>
       <c r="C26" s="19" t="n"/>
       <c r="D26" s="5" t="n">
-        <v>298.75</v>
+        <v>246.903</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="22">
@@ -1088,7 +1077,7 @@
       </c>
       <c r="C27" s="19" t="n"/>
       <c r="D27" s="7" t="n">
-        <v>360.79</v>
+        <v>298.178</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="22">
@@ -1104,7 +1093,7 @@
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="5" t="n">
-        <v>335.59</v>
+        <v>277.349</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="22">
@@ -1120,7 +1109,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="7" t="n">
-        <v>397.65</v>
+        <v>328.637</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="22">
@@ -1136,7 +1125,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="5" t="n">
-        <v>335.59</v>
+        <v>277.349</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="22">
@@ -1152,10 +1141,9 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>397.65</v>
-      </c>
-    </row>
-    <row r="32"/>
+        <v>328.637</v>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -1163,7 +1151,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -1171,33 +1158,27 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="18" customHeight="1" s="22">
       <c r="A42" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
